--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484850_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484850_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.2119</v>
+        <v>8.8264</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2562</v>
+        <v>7.0558</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9557</v>
+        <v>1.7705</v>
       </c>
       <c r="G2" t="n">
         <v>6.7763</v>
@@ -610,13 +610,13 @@
         <v>3.0192</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2244</v>
+        <v>-0.61</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1634</v>
+        <v>-0.3638</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.061</v>
+        <v>-0.2462</v>
       </c>
       <c r="V2" t="n">
         <v>2.4714</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. VAL GUTIERREZ</t>
+          <t>K. FEDOROV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1409</v>
+        <v>5.0842</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7619</v>
+        <v>5.3667</v>
       </c>
       <c r="F3" t="n">
-        <v>1.379</v>
+        <v>-0.2825</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2023</v>
+        <v>5.0547</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1495</v>
+        <v>2.0653</v>
       </c>
       <c r="I3" t="n">
-        <v>4.0528</v>
+        <v>2.9894</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2803</v>
+        <v>5.571</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8992</v>
+        <v>2.8635</v>
       </c>
       <c r="L3" t="n">
-        <v>3.3812</v>
+        <v>2.7075</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.078</v>
+        <v>-0.5163</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7497</v>
+        <v>-0.7982</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6717</v>
+        <v>0.2819</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9435</v>
+        <v>1.887</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0757</v>
+        <v>-1.1322</v>
       </c>
       <c r="R3" t="n">
         <v>3.0192</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3256</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3121</v>
+        <v>-0.3173</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6377</v>
+        <v>-0.295</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3208</v>
+        <v>-1.2452</v>
       </c>
       <c r="W3" t="n">
         <v>1.2452</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.9244</v>
+        <v>-2.4904</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. FEDOROV</t>
+          <t>S. VAL GUTIERREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.9641</v>
+        <v>4.8952</v>
       </c>
       <c r="E4" t="n">
-        <v>5.4053</v>
+        <v>3.4897</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4412</v>
+        <v>1.4055</v>
       </c>
       <c r="G4" t="n">
-        <v>5.0547</v>
+        <v>4.2023</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0653</v>
+        <v>0.1495</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9894</v>
+        <v>4.0528</v>
       </c>
       <c r="J4" t="n">
-        <v>5.571</v>
+        <v>4.2803</v>
       </c>
       <c r="K4" t="n">
-        <v>2.8635</v>
+        <v>0.8992</v>
       </c>
       <c r="L4" t="n">
-        <v>2.7075</v>
+        <v>3.3812</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5163</v>
+        <v>-0.078</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7982</v>
+        <v>-0.7497</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2819</v>
+        <v>0.6717</v>
       </c>
       <c r="P4" t="n">
-        <v>1.887</v>
+        <v>0.9435</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1322</v>
+        <v>-2.0757</v>
       </c>
       <c r="R4" t="n">
         <v>3.0192</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7324000000000001</v>
+        <v>-0.5714</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2787</v>
+        <v>0.0399</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4537</v>
+        <v>-0.6113</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2452</v>
+        <v>0.3208</v>
       </c>
       <c r="W4" t="n">
         <v>1.2452</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.4904</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="5">
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. BLEDA MIRANDA</t>
+          <t>S. MASSAMBA JOHANSSON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6821</v>
+        <v>-0.981</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1828</v>
+        <v>0.2235</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4992</v>
+        <v>-1.2044</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2893</v>
+        <v>0.108</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4797</v>
+        <v>-1.0025</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8096</v>
+        <v>1.1105</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3794</v>
+        <v>0.6551</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-0.6284</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1645</v>
+        <v>1.2836</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9099</v>
+        <v>-0.5471</v>
       </c>
       <c r="N6" t="n">
-        <v>0.06419999999999999</v>
+        <v>-0.3741</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9741</v>
+        <v>-0.173</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9435</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9435</v>
+        <v>0.1887</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2863</v>
+        <v>0.1562</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1052</v>
+        <v>-0.243</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3916</v>
+        <v>0.3992</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6226</v>
+        <v>-1.2452</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.9244</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. MASSAMBA JOHANSSON</t>
+          <t>C. BLEDA MIRANDA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8668</v>
+        <v>-0.9814000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.126</v>
+        <v>-0.0854</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9928</v>
+        <v>-0.8961</v>
       </c>
       <c r="G7" t="n">
-        <v>0.108</v>
+        <v>-1.2893</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0025</v>
+        <v>-0.4797</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1105</v>
+        <v>-0.8096</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6551</v>
+        <v>-0.3794</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6284</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2836</v>
+        <v>0.1645</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5471</v>
+        <v>-0.9099</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3741</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.173</v>
+        <v>-0.9741</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.9435</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1887</v>
+        <v>0.9435</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2704</v>
+        <v>-0.0131</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3404</v>
+        <v>-0.0078</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6108</v>
+        <v>-0.0053</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2452</v>
+        <v>-0.6226</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2452</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6611</v>
+        <v>-1.1021</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.0919</v>
+        <v>-2.8769</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4309</v>
+        <v>1.7748</v>
       </c>
       <c r="G8" t="n">
         <v>-1.6972</v>
@@ -1078,13 +1078,13 @@
         <v>3.2079</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3979</v>
+        <v>-0.839</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3839</v>
+        <v>-0.1689</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.014</v>
+        <v>-0.6701</v>
       </c>
       <c r="V8" t="n">
         <v>0.3018</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. DE ANDREA LUNA</t>
+          <t>G. TUDELA GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7615</v>
+        <v>-2.7984</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9888</v>
+        <v>-2.8435</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7727000000000001</v>
+        <v>0.0451</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.1036</v>
+        <v>-0.2046</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2138</v>
+        <v>-1.123</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8898</v>
+        <v>0.9184</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2369</v>
+        <v>0.4745</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6284</v>
+        <v>0.2277</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6084000000000001</v>
+        <v>0.2468</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8668</v>
+        <v>-0.6791</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5854</v>
+        <v>-1.3507</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2814</v>
+        <v>0.6717</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.6983</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.887</v>
+        <v>-3.0192</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1887</v>
+        <v>2.2644</v>
       </c>
       <c r="S9" t="n">
-        <v>1.0405</v>
+        <v>-0.5939</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1351</v>
+        <v>-0.2988</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0946</v>
+        <v>-0.295</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. TUDELA GARCIA</t>
+          <t>I. DE ANDREA LUNA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1722</v>
+        <v>-3.3906</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0586</v>
+        <v>-2.6708</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1136</v>
+        <v>-0.7198</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2046</v>
+        <v>-2.1036</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.123</v>
+        <v>-1.2138</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9184</v>
+        <v>-0.8898</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4745</v>
+        <v>-1.2369</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2277</v>
+        <v>-0.6284</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2468</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6791</v>
+        <v>-0.8668</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3507</v>
+        <v>-0.5854</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6717</v>
+        <v>-0.2814</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7548</v>
+        <v>-1.6983</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0192</v>
+        <v>-1.887</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2644</v>
+        <v>0.1887</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9676</v>
+        <v>0.4113</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5139</v>
+        <v>0.4531</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4537</v>
+        <v>-0.0417</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9079</v>
+        <v>-4.6988</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4335</v>
+        <v>-1.2773</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.4744</v>
+        <v>-3.4215</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3475</v>
@@ -1312,13 +1312,13 @@
         <v>0.1887</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2587</v>
+        <v>-0.0495</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.164</v>
+        <v>-0.0078</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0946</v>
+        <v>-0.0417</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4904</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.833100000000002</v>
+        <v>6.4213</v>
       </c>
       <c r="E12" t="n">
-        <v>7.361599999999999</v>
+        <v>7.9496</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5283</v>
+        <v>-1.5284</v>
       </c>
       <c r="G12" t="n">
         <v>10.0669</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0001999999999995339</v>
+        <v>0.0001999999999997559</v>
       </c>
       <c r="I12" t="n">
         <v>10.0668</v>
@@ -1372,13 +1372,13 @@
         <v>10.1722</v>
       </c>
       <c r="M12" t="n">
-        <v>-6.7805</v>
+        <v>-6.780500000000001</v>
       </c>
       <c r="N12" t="n">
         <v>-6.6754</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1051000000000002</v>
+        <v>-0.1051000000000001</v>
       </c>
       <c r="P12" t="n">
         <v>2.8305</v>
@@ -1390,16 +1390,16 @@
         <v>16.0395</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.3094</v>
+        <v>-2.7218</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.5023</v>
+        <v>-0.9143999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.8069</v>
+        <v>-1.8071</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.7546</v>
+        <v>-3.754600000000001</v>
       </c>
       <c r="W12" t="n">
         <v>5.2256</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.2425</v>
+        <v>6.0356</v>
       </c>
       <c r="E13" t="n">
-        <v>6.7952</v>
+        <v>6.4055</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5527</v>
+        <v>-0.3699</v>
       </c>
       <c r="G13" t="n">
         <v>3.6192</v>
@@ -1468,13 +1468,13 @@
         <v>2.2644</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9817</v>
+        <v>0.7748</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7265</v>
+        <v>0.3367</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2552</v>
+        <v>0.438</v>
       </c>
       <c r="V13" t="n">
         <v>1.2642</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9988</v>
+        <v>0.8545</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3986</v>
+        <v>1.2037</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3998</v>
+        <v>-0.3492</v>
       </c>
       <c r="G15" t="n">
         <v>-2.9663</v>
@@ -1624,13 +1624,13 @@
         <v>2.4531</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1163</v>
+        <v>0.972</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6212</v>
+        <v>0.4264</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4951</v>
+        <v>0.5456</v>
       </c>
       <c r="V15" t="n">
         <v>2.4714</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.119</v>
+        <v>0.4378</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2054</v>
+        <v>0.4977</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0864</v>
+        <v>-0.0599</v>
       </c>
       <c r="G16" t="n">
         <v>-0.1416</v>
@@ -1702,13 +1702,13 @@
         <v>0.1887</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2299</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1176</v>
+        <v>0.1747</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1123</v>
+        <v>-0.0858</v>
       </c>
       <c r="V16" t="n">
         <v>0.3018</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.034</v>
+        <v>-0.1445</v>
       </c>
       <c r="E17" t="n">
         <v>-1.7185</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6845</v>
+        <v>1.574</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6766</v>
@@ -1780,13 +1780,13 @@
         <v>2.2644</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0958</v>
+        <v>0.9852</v>
       </c>
       <c r="T17" t="n">
         <v>0.2068</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8889</v>
+        <v>0.7784</v>
       </c>
       <c r="V17" t="n">
         <v>1.2452</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. ALFEREZ CANSECO</t>
+          <t>B. ZHENG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1153</v>
+        <v>-0.2734</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0177</v>
+        <v>-0.0751</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0977</v>
+        <v>-0.1983</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0742</v>
+        <v>0.4658</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2927</v>
+        <v>0.5807</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7815</v>
+        <v>-0.1149</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0411</v>
+        <v>1.1919</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.5494</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0411</v>
+        <v>0.6425</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1153</v>
+        <v>-0.7261</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2927</v>
+        <v>0.0313</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8226</v>
+        <v>-0.7574</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.1887</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1322</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.3209</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0412</v>
+        <v>-0.0225</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0588</v>
+        <v>-0.1348</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0176</v>
+        <v>0.1123</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.9054</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.9054</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. ZHENG</t>
+          <t>D. ALFEREZ CANSECO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2344</v>
+        <v>-1.0889</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5623</v>
+        <v>-0.0177</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6721</v>
+        <v>-1.0712</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4658</v>
+        <v>-1.0742</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5807</v>
+        <v>-0.2927</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1149</v>
+        <v>-0.7815</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1919</v>
+        <v>0.0411</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5494</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6425</v>
+        <v>0.0411</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7261</v>
+        <v>-1.1153</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0313</v>
+        <v>-0.2927</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7574</v>
+        <v>-0.8226</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1887</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1322</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3209</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9835</v>
+        <v>-0.0147</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.622</v>
+        <v>-0.0588</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3615</v>
+        <v>0.0441</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9054</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.9054</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. ALAMINOS HERNANDEZ</t>
+          <t>J. NUNEZ NIEVAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5481</v>
+        <v>-1.1881</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9812</v>
+        <v>-0.8603</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5669</v>
+        <v>-0.3279</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.4634</v>
+        <v>-2.6427</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5799</v>
+        <v>-1.6661</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.8835</v>
+        <v>-0.9766</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.278</v>
+        <v>-0.9141</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6284</v>
+        <v>-0.9978</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6496</v>
+        <v>0.0837</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1854</v>
+        <v>-1.7286</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0485</v>
+        <v>-0.6683</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2339</v>
+        <v>-1.0603</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3774</v>
+        <v>0.9435</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1322</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3774</v>
+        <v>2.0757</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5379</v>
+        <v>0.5111</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2968</v>
+        <v>-0.0592</v>
       </c>
       <c r="U20" t="n">
-        <v>0.241</v>
+        <v>0.5703</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. MARTIN MARTINEZ</t>
+          <t>I. ALAMINOS HERNANDEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7543</v>
+        <v>-1.8223</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0863</v>
+        <v>-1.176</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.668</v>
+        <v>-0.6463</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.4985</v>
+        <v>-2.4634</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.5873</v>
+        <v>-0.5799</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0888</v>
+        <v>-1.8835</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.0404</v>
+        <v>-1.278</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.1723</v>
+        <v>-0.6284</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1319</v>
+        <v>-0.6496</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.458</v>
+        <v>-1.1854</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4149</v>
+        <v>0.0485</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0431</v>
+        <v>-1.2339</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9435</v>
+        <v>0.3774</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9435</v>
+        <v>0.3774</v>
       </c>
       <c r="S21" t="n">
-        <v>1.6877</v>
+        <v>0.2636</v>
       </c>
       <c r="T21" t="n">
-        <v>1.596</v>
+        <v>0.102</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0917</v>
+        <v>0.1617</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. NUNEZ NIEVAS</t>
+          <t>G. GARCIA CARCASES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5546</v>
+        <v>-2.2136</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8346</v>
+        <v>-0.6994</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.72</v>
+        <v>-1.5143</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.6427</v>
+        <v>-0.482</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6661</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9766</v>
+        <v>0.3421</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9141</v>
+        <v>0.4608</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9978</v>
+        <v>-0.2058</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0837</v>
+        <v>0.6666</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.7286</v>
+        <v>-0.9428</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6683</v>
+        <v>-0.6182</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0603</v>
+        <v>-0.3245</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9435</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.1322</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0757</v>
+        <v>0.7548</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8552999999999999</v>
+        <v>-0.109</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0335</v>
+        <v>-0.0279</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1782</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>-1.2452</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G. GARCIA CARCASES</t>
+          <t>M. MARTIN MARTINEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7236</v>
+        <v>-2.6516</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8942</v>
+        <v>-1.0606</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8294</v>
+        <v>-1.591</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.482</v>
+        <v>-2.4985</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8241000000000001</v>
+        <v>-2.5873</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3421</v>
+        <v>0.0888</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4608</v>
+        <v>-1.0404</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2058</v>
+        <v>-1.1723</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6666</v>
+        <v>0.1319</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9428</v>
+        <v>-1.458</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6182</v>
+        <v>-1.4149</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3245</v>
+        <v>-0.0431</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3774</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1322</v>
+        <v>-1.887</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7548</v>
+        <v>0.9435</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.619</v>
+        <v>0.7904</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2228</v>
+        <v>0.6216</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3962</v>
+        <v>0.1687</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X23" t="n">
         <v>-1.2452</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4802</v>
+        <v>-3.7304</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0269</v>
+        <v>-2.2218</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4533</v>
+        <v>-1.5086</v>
       </c>
       <c r="G24" t="n">
         <v>-2.4575</v>
@@ -2326,13 +2326,13 @@
         <v>0.5661</v>
       </c>
       <c r="S24" t="n">
-        <v>0.619</v>
+        <v>0.3689</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4144</v>
+        <v>0.2195</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2046</v>
+        <v>0.1493</v>
       </c>
       <c r="V24" t="n">
         <v>0.6226</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.833299999999999</v>
+        <v>-4.534000000000002</v>
       </c>
       <c r="E25" t="n">
-        <v>1.528400000000002</v>
+        <v>1.5284</v>
       </c>
       <c r="F25" t="n">
-        <v>-7.361799999999999</v>
+        <v>-6.0626</v>
       </c>
       <c r="G25" t="n">
         <v>-10.0669</v>
@@ -2377,13 +2377,13 @@
         <v>-10.0669</v>
       </c>
       <c r="J25" t="n">
-        <v>6.780599999999998</v>
+        <v>6.7806</v>
       </c>
       <c r="K25" t="n">
-        <v>6.675600000000001</v>
+        <v>6.675599999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1050999999999998</v>
+        <v>0.1050999999999997</v>
       </c>
       <c r="M25" t="n">
         <v>-16.8474</v>
@@ -2404,19 +2404,19 @@
         <v>13.209</v>
       </c>
       <c r="S25" t="n">
-        <v>3.3095</v>
+        <v>4.608700000000001</v>
       </c>
       <c r="T25" t="n">
         <v>1.807</v>
       </c>
       <c r="U25" t="n">
-        <v>1.5023</v>
+        <v>2.8015</v>
       </c>
       <c r="V25" t="n">
         <v>3.7546</v>
       </c>
       <c r="W25" t="n">
-        <v>8.980200000000002</v>
+        <v>8.9802</v>
       </c>
       <c r="X25" t="n">
         <v>-5.2256</v>
